--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
   </si>
   <si>
     <t xml:space="preserve">Cet attribut représente la structure de l’auteur. 
-Pour les documents d’expression personnelle du patient, cette métadonnée est absente, cela signifie que l’élément XML &lt;rim:Slot name='authorInstitution'&gt; n’est pas transmis. </t>
+Pour les documents d’expression personnelle du patient, cette métadonnée est absente, cela signifie que l’élément XML `&lt;rim:Slot name='authorInstitution'&gt;` n’est pas transmis. </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -292,7 +292,7 @@
     <t>Autorité d’affectation</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifiant de l’organisme gérant l’identifiant de la structure. Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes. </t>
+    <t>Identifiant de l’organisme gérant l’identifiant de la structure. Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes.</t>
   </si>
   <si>
     <t>xdm-author-institution.XON6.composant1</t>
@@ -342,7 +342,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Identifiant de la structure (Struct_IdNat)</t>
+    <t>Identifiant de la structure (Struct_IdNat)</t>
   </si>
   <si>
     <t>author/assignedAuthor/representedOrganization/id@extension</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-institution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
